--- a/data/xpclr/genes_annotattion_manhattan_plot.xlsx
+++ b/data/xpclr/genes_annotattion_manhattan_plot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/xpclr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C407767-A7E5-DC45-9895-64AF892BA125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF294D09-D70C-8B4E-AE94-3D2444A1025A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{56045F81-525B-3E4B-A49F-8143DC5B735D}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15760" xr2:uid="{56045F81-525B-3E4B-A49F-8143DC5B735D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
   <si>
     <t>comparison</t>
   </si>
@@ -203,13 +203,13 @@
     <t>GOGAT</t>
   </si>
   <si>
-    <t>Sobic.001G090900</t>
-  </si>
-  <si>
-    <t>Seed maturation protein</t>
-  </si>
-  <si>
     <t>GDH</t>
+  </si>
+  <si>
+    <t>dot_color</t>
+  </si>
+  <si>
+    <t>Red</t>
   </si>
 </sst>
 </file>
@@ -588,13 +588,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED83C7D5-C5B7-0643-A2ED-7C45D680692B}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,8 +631,11 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -672,8 +675,11 @@
       <c r="M2" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N2" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -711,10 +717,13 @@
         <v>18</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -752,10 +761,13 @@
         <v>20</v>
       </c>
       <c r="M4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -793,10 +805,13 @@
         <v>22</v>
       </c>
       <c r="M5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -834,10 +849,13 @@
         <v>24</v>
       </c>
       <c r="M6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -875,10 +893,13 @@
         <v>26</v>
       </c>
       <c r="M7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -916,10 +937,13 @@
         <v>28</v>
       </c>
       <c r="M8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -957,10 +981,13 @@
         <v>30</v>
       </c>
       <c r="M9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -998,10 +1025,13 @@
         <v>32</v>
       </c>
       <c r="M10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1038,9 +1068,55 @@
       <c r="L11" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>9260001</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9335000</v>
+      </c>
+      <c r="E12" s="1">
+        <v>359.78459939999999</v>
+      </c>
+      <c r="F12" s="1">
+        <v>7</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9314865</v>
+      </c>
+      <c r="I12" s="1">
+        <v>9324191</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1048,286 +1124,221 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>9260001</v>
+        <v>10060001</v>
       </c>
       <c r="D13" s="1">
-        <v>9335000</v>
+        <v>10175000</v>
       </c>
       <c r="E13" s="1">
-        <v>359.78459939999999</v>
+        <v>440.0505579</v>
       </c>
       <c r="F13" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>9314865</v>
+        <v>10149646</v>
       </c>
       <c r="I13" s="1">
-        <v>9324191</v>
+        <v>10155743</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1">
-        <v>10060001</v>
+        <v>76640001</v>
       </c>
       <c r="D14" s="1">
-        <v>10175000</v>
+        <v>76770000</v>
       </c>
       <c r="E14" s="1">
-        <v>440.0505579</v>
+        <v>439.29488240000001</v>
       </c>
       <c r="F14" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="1">
-        <v>10149646</v>
+        <v>76638171</v>
       </c>
       <c r="I14" s="1">
-        <v>10155743</v>
+        <v>76657673</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>76640001</v>
+        <v>69815001</v>
       </c>
       <c r="D15" s="1">
-        <v>76770000</v>
+        <v>69840000</v>
       </c>
       <c r="E15" s="1">
-        <v>439.29488240000001</v>
+        <v>382.0350067</v>
       </c>
       <c r="F15" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="1">
-        <v>76638171</v>
+        <v>69822503</v>
       </c>
       <c r="I15" s="1">
-        <v>76657673</v>
+        <v>69829458</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1">
-        <v>69815001</v>
+        <v>320001</v>
       </c>
       <c r="D16" s="1">
-        <v>69840000</v>
+        <v>345000</v>
       </c>
       <c r="E16" s="1">
-        <v>382.0350067</v>
+        <v>186.00673019999999</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="1">
-        <v>69822503</v>
+        <v>315828</v>
       </c>
       <c r="I16" s="1">
-        <v>69829458</v>
+        <v>328539</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1">
-        <v>320001</v>
+        <v>59645001</v>
       </c>
       <c r="D17" s="1">
-        <v>345000</v>
+        <v>59705000</v>
       </c>
       <c r="E17" s="1">
-        <v>186.00673019999999</v>
+        <v>624.1662986</v>
       </c>
       <c r="F17" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H17" s="1">
-        <v>315828</v>
+        <v>59678213</v>
       </c>
       <c r="I17" s="1">
-        <v>328539</v>
+        <v>59684263</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1">
-        <v>7</v>
-      </c>
-      <c r="C18" s="1">
-        <v>59645001</v>
-      </c>
-      <c r="D18" s="1">
-        <v>59705000</v>
-      </c>
-      <c r="E18" s="1">
-        <v>624.1662986</v>
-      </c>
-      <c r="F18" s="1">
-        <v>5</v>
-      </c>
-      <c r="G18" s="1">
-        <v>7</v>
-      </c>
-      <c r="H18" s="1">
-        <v>59678213</v>
-      </c>
-      <c r="I18" s="1">
-        <v>59684263</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>7020001</v>
-      </c>
-      <c r="D19">
-        <v>7185000</v>
-      </c>
-      <c r="E19">
-        <v>820.54433840000002</v>
-      </c>
-      <c r="F19">
-        <v>9</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>7116123</v>
-      </c>
-      <c r="I19">
-        <v>7121070</v>
-      </c>
-      <c r="J19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" t="s">
-        <v>55</v>
-      </c>
-      <c r="L19" t="s">
-        <v>56</v>
-      </c>
-      <c r="M19" s="1"/>
-    </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M18" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/xpclr/genes_annotattion_manhattan_plot.xlsx
+++ b/data/xpclr/genes_annotattion_manhattan_plot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/xpclr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF294D09-D70C-8B4E-AE94-3D2444A1025A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B135D42A-7507-1B4D-84E7-C2F249CBED2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15760" xr2:uid="{56045F81-525B-3E4B-A49F-8143DC5B735D}"/>
+    <workbookView xWindow="27040" yWindow="-5200" windowWidth="51200" windowHeight="28180" xr2:uid="{56045F81-525B-3E4B-A49F-8143DC5B735D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="65">
   <si>
     <t>comparison</t>
   </si>
@@ -137,9 +137,6 @@
     <t>K-box region</t>
   </si>
   <si>
-    <t>Sobic.007G078200</t>
-  </si>
-  <si>
     <t>breeding_improved_vs_landrace</t>
   </si>
   <si>
@@ -194,9 +191,6 @@
     <t>MADS</t>
   </si>
   <si>
-    <t>Terpene</t>
-  </si>
-  <si>
     <t>CKX</t>
   </si>
   <si>
@@ -209,19 +203,52 @@
     <t>dot_color</t>
   </si>
   <si>
-    <t>Red</t>
+    <t>#FF7F00</t>
+  </si>
+  <si>
+    <t>#B15928</t>
+  </si>
+  <si>
+    <t>#6A3D9A</t>
+  </si>
+  <si>
+    <t>Sobic.001G074700</t>
+  </si>
+  <si>
+    <t>Belongs to the cytochrome c oxidase subunit 6A family</t>
+  </si>
+  <si>
+    <t>Sobic.001G264700</t>
+  </si>
+  <si>
+    <t>PPIases accelerate the folding of proteins. It catalyzes the cis-trans isomerization of proline imidic peptide bonds in oligopeptides</t>
+  </si>
+  <si>
+    <t>#33a02c</t>
+  </si>
+  <si>
+    <t>pplase</t>
+  </si>
+  <si>
+    <t>cyp</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -251,9 +278,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -592,6 +620,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="147.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -632,268 +662,268 @@
         <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>4410001</v>
+        <v>9260001</v>
       </c>
       <c r="D2" s="1">
-        <v>4540000</v>
+        <v>9335000</v>
       </c>
       <c r="E2" s="1">
-        <v>682.31204809999997</v>
+        <v>359.78459939999999</v>
       </c>
       <c r="F2" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>4486981</v>
+        <v>9314865</v>
       </c>
       <c r="I2" s="1">
-        <v>4497443</v>
+        <v>9324191</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>9555001</v>
+        <v>10060001</v>
       </c>
       <c r="D3" s="1">
-        <v>9640000</v>
+        <v>10175000</v>
       </c>
       <c r="E3" s="1">
-        <v>445.61171200000001</v>
+        <v>440.0505579</v>
       </c>
       <c r="F3" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <v>9576725</v>
+        <v>10149646</v>
       </c>
       <c r="I3" s="1">
-        <v>9581867</v>
+        <v>10155743</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>63965001</v>
+        <v>5705001</v>
       </c>
       <c r="D4" s="1">
-        <v>64085000</v>
+        <v>5785000</v>
       </c>
       <c r="E4" s="1">
-        <v>1427.85014</v>
+        <v>243.36559969999999</v>
       </c>
       <c r="F4" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
       </c>
       <c r="H4" s="1">
-        <v>63984699</v>
+        <v>5741915</v>
       </c>
       <c r="I4" s="1">
-        <v>63991441</v>
+        <v>5748892</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>70035001</v>
+        <v>53640001</v>
       </c>
       <c r="D5" s="1">
-        <v>70315000</v>
+        <v>53665000</v>
       </c>
       <c r="E5" s="1">
-        <v>632.62153860000001</v>
+        <v>144.8218306</v>
       </c>
       <c r="F5" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>70197748</v>
+        <v>53635710</v>
       </c>
       <c r="I5" s="1">
-        <v>70205378</v>
+        <v>53640841</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>2195001</v>
+        <v>76640001</v>
       </c>
       <c r="D6" s="1">
-        <v>2250000</v>
+        <v>76770000</v>
       </c>
       <c r="E6" s="1">
-        <v>578.18597399999999</v>
+        <v>439.29488240000001</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>2247547</v>
+        <v>76638171</v>
       </c>
       <c r="I6" s="1">
-        <v>2254217</v>
+        <v>76657673</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>66615001</v>
+        <v>69815001</v>
       </c>
       <c r="D7" s="1">
-        <v>66695000</v>
+        <v>69840000</v>
       </c>
       <c r="E7" s="1">
-        <v>591.89093549999996</v>
+        <v>382.0350067</v>
       </c>
       <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
         <v>3</v>
       </c>
-      <c r="G7" s="1">
-        <v>4</v>
-      </c>
       <c r="H7" s="1">
-        <v>66688183</v>
+        <v>69822503</v>
       </c>
       <c r="I7" s="1">
-        <v>66695948</v>
+        <v>69829458</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>49</v>
@@ -901,90 +931,90 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1">
-        <v>68230001</v>
+        <v>320001</v>
       </c>
       <c r="D8" s="1">
-        <v>68400000</v>
+        <v>345000</v>
       </c>
       <c r="E8" s="1">
-        <v>910.11990070000002</v>
+        <v>186.00673019999999</v>
       </c>
       <c r="F8" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
         <v>4</v>
       </c>
       <c r="H8" s="1">
-        <v>68398377</v>
+        <v>315828</v>
       </c>
       <c r="I8" s="1">
-        <v>68409236</v>
+        <v>328539</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>57</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1">
+        <v>59645001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>59705000</v>
+      </c>
+      <c r="E9" s="1">
+        <v>624.1662986</v>
+      </c>
+      <c r="F9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="1">
-        <v>6220001</v>
-      </c>
-      <c r="D9" s="1">
-        <v>6260000</v>
-      </c>
-      <c r="E9" s="1">
-        <v>868.80371449999996</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2</v>
-      </c>
       <c r="G9" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H9" s="1">
-        <v>6225254</v>
+        <v>59678213</v>
       </c>
       <c r="I9" s="1">
-        <v>6231031</v>
+        <v>59684263</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -992,43 +1022,43 @@
         <v>12</v>
       </c>
       <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4410001</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4540000</v>
+      </c>
+      <c r="E10" s="1">
+        <v>682.31204809999997</v>
+      </c>
+      <c r="F10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" s="1">
-        <v>48970001</v>
-      </c>
-      <c r="D10" s="1">
-        <v>49155000</v>
-      </c>
-      <c r="E10" s="1">
-        <v>554.79709769999999</v>
-      </c>
-      <c r="F10" s="1">
-        <v>7</v>
-      </c>
       <c r="G10" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>49101780</v>
+        <v>4486981</v>
       </c>
       <c r="I10" s="1">
-        <v>49128077</v>
+        <v>4497443</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -1036,310 +1066,357 @@
         <v>12</v>
       </c>
       <c r="B11" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>9145001</v>
+        <v>9555001</v>
       </c>
       <c r="D11" s="1">
-        <v>9260000</v>
+        <v>9640000</v>
       </c>
       <c r="E11" s="1">
-        <v>794.22554969999999</v>
+        <v>445.61171200000001</v>
       </c>
       <c r="F11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>9139649</v>
+        <v>9576725</v>
       </c>
       <c r="I11" s="1">
-        <v>9152606</v>
+        <v>9581867</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>9260001</v>
+        <v>63965001</v>
       </c>
       <c r="D12" s="1">
-        <v>9335000</v>
+        <v>64085000</v>
       </c>
       <c r="E12" s="1">
-        <v>359.78459939999999</v>
+        <v>1427.85014</v>
       </c>
       <c r="F12" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
       </c>
       <c r="H12" s="1">
-        <v>9314865</v>
+        <v>63984699</v>
       </c>
       <c r="I12" s="1">
-        <v>9324191</v>
+        <v>63991441</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>10060001</v>
+        <v>70035001</v>
       </c>
       <c r="D13" s="1">
-        <v>10175000</v>
+        <v>70315000</v>
       </c>
       <c r="E13" s="1">
-        <v>440.0505579</v>
+        <v>632.62153860000001</v>
       </c>
       <c r="F13" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>10149646</v>
+        <v>70197748</v>
       </c>
       <c r="I13" s="1">
-        <v>10155743</v>
+        <v>70205378</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>57</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1">
-        <v>76640001</v>
+        <v>2195001</v>
       </c>
       <c r="D14" s="1">
-        <v>76770000</v>
+        <v>2250000</v>
       </c>
       <c r="E14" s="1">
-        <v>439.29488240000001</v>
+        <v>578.18597399999999</v>
       </c>
       <c r="F14" s="1">
         <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="1">
-        <v>76638171</v>
+        <v>2247547</v>
       </c>
       <c r="I14" s="1">
-        <v>76657673</v>
+        <v>2254217</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1">
+        <v>66615001</v>
+      </c>
+      <c r="D15" s="1">
+        <v>66695000</v>
+      </c>
+      <c r="E15" s="1">
+        <v>591.89093549999996</v>
+      </c>
+      <c r="F15" s="1">
         <v>3</v>
       </c>
-      <c r="C15" s="1">
-        <v>69815001</v>
-      </c>
-      <c r="D15" s="1">
-        <v>69840000</v>
-      </c>
-      <c r="E15" s="1">
-        <v>382.0350067</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
       <c r="G15" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="1">
-        <v>69822503</v>
+        <v>66688183</v>
       </c>
       <c r="I15" s="1">
-        <v>69829458</v>
+        <v>66695948</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1">
         <v>4</v>
       </c>
       <c r="C16" s="1">
-        <v>320001</v>
+        <v>68230001</v>
       </c>
       <c r="D16" s="1">
-        <v>345000</v>
+        <v>68400000</v>
       </c>
       <c r="E16" s="1">
-        <v>186.00673019999999</v>
+        <v>910.11990070000002</v>
       </c>
       <c r="F16" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G16" s="1">
         <v>4</v>
       </c>
       <c r="H16" s="1">
-        <v>315828</v>
+        <v>68398377</v>
       </c>
       <c r="I16" s="1">
-        <v>328539</v>
+        <v>68409236</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6220001</v>
+      </c>
+      <c r="D17" s="1">
+        <v>6260000</v>
+      </c>
+      <c r="E17" s="1">
+        <v>868.80371449999996</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>6225254</v>
+      </c>
+      <c r="I17" s="1">
+        <v>6231031</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1">
+        <v>48970001</v>
+      </c>
+      <c r="D18" s="1">
+        <v>49155000</v>
+      </c>
+      <c r="E18" s="1">
+        <v>554.79709769999999</v>
+      </c>
+      <c r="F18" s="1">
         <v>7</v>
       </c>
-      <c r="C17" s="1">
-        <v>59645001</v>
-      </c>
-      <c r="D17" s="1">
-        <v>59705000</v>
-      </c>
-      <c r="E17" s="1">
-        <v>624.1662986</v>
-      </c>
-      <c r="F17" s="1">
-        <v>5</v>
-      </c>
-      <c r="G17" s="1">
-        <v>7</v>
-      </c>
-      <c r="H17" s="1">
-        <v>59678213</v>
-      </c>
-      <c r="I17" s="1">
-        <v>59684263</v>
-      </c>
-      <c r="J17" s="1" t="s">
+      <c r="G18" s="1">
+        <v>6</v>
+      </c>
+      <c r="H18" s="1">
+        <v>49101780</v>
+      </c>
+      <c r="I18" s="1">
+        <v>49128077</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M17" s="1" t="s">
+      <c r="K18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="M18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N19">
+    <sortCondition ref="A1:A19"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>